--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>preparation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_Preparation}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_Preparation|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -822,7 +822,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -920,7 +920,7 @@
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -956,7 +956,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -984,7 +984,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1003,7 +1003,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1086,7 +1086,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1105,7 +1105,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType|3.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -1176,7 +1176,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1274,7 +1274,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1319,7 +1319,7 @@
     <t>MedicationDispense.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1399,7 +1399,7 @@
     <t>処方箋で正確に指定されているように、製品以外に異なる薬物が分配されるかどうかを説明するコード化された概念。 / A coded concept describing whether a different medicinal product may be dispensed other than the product as specified exactly in the prescription.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode|3.0.0</t>
   </si>
   <si>
     <t>CombinedMedicationDispense.substitutionMade.code</t>
@@ -1420,7 +1420,7 @@
     <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1432,7 +1432,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1455,7 +1455,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1475,7 +1475,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1805,7 +1805,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="252.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,7 +1820,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>preparation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_Preparation|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_Preparation}
 </t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -822,7 +822,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue|4.0.1)</t>
+Reference(DetectedIssue)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -920,7 +920,7 @@
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
 </t>
   </si>
   <si>
@@ -956,7 +956,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -984,7 +984,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1003,7 +1003,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1086,7 +1086,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1105,7 +1105,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection)
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
     <t>.code</t>
@@ -1176,7 +1176,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1274,7 +1274,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -1319,7 +1319,7 @@
     <t>MedicationDispense.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection|1.3.0-dev}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection}
 </t>
   </si>
   <si>
@@ -1399,7 +1399,7 @@
     <t>処方箋で正確に指定されているように、製品以外に異なる薬物が分配されるかどうかを説明するコード化された概念。 / A coded concept describing whether a different medicinal product may be dispensed other than the product as specified exactly in the prescription.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
   </si>
   <si>
     <t>CombinedMedicationDispense.substitutionMade.code</t>
@@ -1420,7 +1420,7 @@
     <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1432,7 +1432,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -1455,7 +1455,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
+    <t xml:space="preserve">Reference(DetectedIssue)
 </t>
   </si>
   <si>
@@ -1475,7 +1475,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -1805,7 +1805,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="252.4765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,7 +1820,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
